--- a/data/trans_orig/Q5406-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2007</t>
+          <t>Población según si es capaz de tomar medicación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99171</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110283</t>
+          <t>110353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131764</t>
+          <t>130925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144954</t>
+          <t>145003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235341</t>
+          <t>235697</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252145</t>
+          <t>252103</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>13943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128487</t>
+          <t>128554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140128</t>
+          <t>140784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158425</t>
+          <t>158573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174538</t>
+          <t>174968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293257</t>
+          <t>293181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312720</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93250</t>
+          <t>93774</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>103349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118690</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217997</t>
+          <t>217943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233166</t>
+          <t>232892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22926</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123876</t>
+          <t>123742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133852</t>
+          <t>133122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>190234</t>
+          <t>191059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>204255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317974</t>
+          <t>318262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335109</t>
+          <t>335050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69796</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458808</t>
+          <t>458908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>479484</t>
+          <t>479717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>618481</t>
+          <t>619463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>645241</t>
+          <t>645182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1087766</t>
+          <t>1086078</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1119455</t>
+          <t>1120894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2012</t>
+          <t>Población según si es capaz de tomar medicación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118981</t>
+          <t>118893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134124</t>
+          <t>134258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141950</t>
+          <t>140857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157484</t>
+          <t>156837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>267112</t>
+          <t>267519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>288535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17736</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128700</t>
+          <t>129485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146174</t>
+          <t>146048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152672</t>
+          <t>152827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172619</t>
+          <t>171940</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289797</t>
+          <t>287631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>315630</t>
+          <t>314554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81590</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97179</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111142</t>
+          <t>110663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128667</t>
+          <t>128619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198914</t>
+          <t>199226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222203</t>
+          <t>222369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38014</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136670</t>
+          <t>134536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153369</t>
+          <t>152535</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212533</t>
+          <t>213682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>230981</t>
+          <t>231367</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356966</t>
+          <t>357403</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380410</t>
+          <t>380703</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46458</t>
+          <t>43950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68343</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>69131</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110576</t>
+          <t>107561</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>485441</t>
+          <t>488591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>518208</t>
+          <t>520073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>638744</t>
+          <t>638025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>674492</t>
+          <t>674913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1139370</t>
+          <t>1138544</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1185609</t>
+          <t>1187332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2016</t>
+          <t>Población según si es capaz de tomar medicación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120415</t>
+          <t>120634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131931</t>
+          <t>131794</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153204</t>
+          <t>152893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167586</t>
+          <t>167447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>277998</t>
+          <t>278773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>296760</t>
+          <t>296688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>152238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161657</t>
+          <t>161612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>193254</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>210688</t>
+          <t>211675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350898</t>
+          <t>350721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370790</t>
+          <t>371170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>101708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112254</t>
+          <t>112237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120958</t>
+          <t>120281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136418</t>
+          <t>136105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227592</t>
+          <t>227982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245817</t>
+          <t>246072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -7125,97 +7125,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8717</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8355</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7669</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167868</t>
+          <t>166728</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>215377</t>
+          <t>215725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234605</t>
+          <t>235247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>388421</t>
+          <t>387644</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>407346</t>
+          <t>408050</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43906</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>556532</t>
+          <t>556935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574821</t>
+          <t>574788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>706155</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>738860</t>
+          <t>736535</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1269472</t>
+          <t>1270660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1306339</t>
+          <t>1306742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2023</t>
+          <t>Población según si es capaz de tomar medicación en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>30895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>130264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140815</t>
+          <t>140682</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153502</t>
+          <t>153188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164309</t>
+          <t>164225</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>288405</t>
+          <t>287353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>303041</t>
+          <t>302543</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146684</t>
+          <t>146385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155696</t>
+          <t>155222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187015</t>
+          <t>186402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200452</t>
+          <t>200023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336981</t>
+          <t>336676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352700</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,82 +9196,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13769</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>11322</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14724</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>12653</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,82 +9309,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12591</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32498</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>16887</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4851</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>32160</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>6,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12591</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31534</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16887</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>32382</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128094</t>
+          <t>126760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135300</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316227</t>
+          <t>315326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356013</t>
+          <t>355174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>454885</t>
+          <t>456087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490649</t>
+          <t>490503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195881</t>
+          <t>196324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202557</t>
+          <t>202531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252640</t>
+          <t>252674</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264156</t>
+          <t>264284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>452261</t>
+          <t>452386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465494</t>
+          <t>465364</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>35457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>41530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>611313</t>
+          <t>611514</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>628881</t>
+          <t>628300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>989312</t>
+          <t>995333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1553556</t>
+          <t>1553281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1615413</t>
+          <t>1611627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5406-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Habitat-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>99599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110353</t>
+          <t>110411</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130925</t>
+          <t>130842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145003</t>
+          <t>144230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235697</t>
+          <t>235540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252103</t>
+          <t>252453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128554</t>
+          <t>128258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140784</t>
+          <t>140221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158573</t>
+          <t>158749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174968</t>
+          <t>174901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>293181</t>
+          <t>292503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312976</t>
+          <t>312557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93774</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103349</t>
+          <t>102660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119976</t>
+          <t>120737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131755</t>
+          <t>132318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217943</t>
+          <t>215883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232892</t>
+          <t>232716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,47 +2136,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8796</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123742</t>
+          <t>123913</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133122</t>
+          <t>133180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191059</t>
+          <t>190250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204255</t>
+          <t>204184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>318262</t>
+          <t>319327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335050</t>
+          <t>335330</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>458908</t>
+          <t>457728</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>479717</t>
+          <t>479103</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>619463</t>
+          <t>617242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>645162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1086078</t>
+          <t>1087961</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1120894</t>
+          <t>1119725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118893</t>
+          <t>119676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134258</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140857</t>
+          <t>141566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156837</t>
+          <t>157309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>267519</t>
+          <t>268675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288535</t>
+          <t>288378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>16507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23567</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129485</t>
+          <t>130602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146048</t>
+          <t>146517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152827</t>
+          <t>153942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171940</t>
+          <t>173795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287631</t>
+          <t>290597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314554</t>
+          <t>315060</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82084</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>111294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128619</t>
+          <t>128997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199226</t>
+          <t>199878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>222369</t>
+          <t>222267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35603</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134536</t>
+          <t>135400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>152535</t>
+          <t>152717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>213682</t>
+          <t>213879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231367</t>
+          <t>231209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357403</t>
+          <t>356534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380703</t>
+          <t>380840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>70478</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107561</t>
+          <t>106655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488591</t>
+          <t>487365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>520073</t>
+          <t>519776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>638025</t>
+          <t>640420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>674913</t>
+          <t>676420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1138544</t>
+          <t>1143677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1187332</t>
+          <t>1188050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120634</t>
+          <t>121125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131794</t>
+          <t>131855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152893</t>
+          <t>153553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167447</t>
+          <t>167421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278773</t>
+          <t>279467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>296688</t>
+          <t>296705</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>23040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>151339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161612</t>
+          <t>161608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>193390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211675</t>
+          <t>210895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>350721</t>
+          <t>351713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371170</t>
+          <t>371353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101708</t>
+          <t>102314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>112223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120281</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136105</t>
+          <t>136141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227982</t>
+          <t>227860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246072</t>
+          <t>246126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166728</t>
+          <t>166685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>215725</t>
+          <t>214358</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>235247</t>
+          <t>234663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387644</t>
+          <t>387113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>408050</t>
+          <t>407990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>76591</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>556935</t>
+          <t>555653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574788</t>
+          <t>574168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>704444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>736535</t>
+          <t>737223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1270660</t>
+          <t>1269943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1307436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136299</t>
+          <t>151051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130264</t>
+          <t>145056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140682</t>
+          <t>155835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159672</t>
+          <t>170594</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153188</t>
+          <t>163846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164225</t>
+          <t>176138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>295971</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>287353</t>
+          <t>312639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302543</t>
+          <t>328409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>151843</t>
+          <t>169695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>164762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155222</t>
+          <t>173130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>193920</t>
+          <t>215336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186402</t>
+          <t>207242</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200023</t>
+          <t>221601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>345762</t>
+          <t>385031</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336676</t>
+          <t>375168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>393017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132656</t>
+          <t>155154</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>149571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135259</t>
+          <t>157940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>342299</t>
+          <t>155828</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315326</t>
+          <t>148902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355174</t>
+          <t>161934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>474955</t>
+          <t>310982</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>456087</t>
+          <t>302225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490503</t>
+          <t>317736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496755</t>
+          <t>334226</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496755</t>
+          <t>334226</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496755</t>
+          <t>334226</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,17 +9667,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>200085</t>
+          <t>209669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196324</t>
+          <t>205295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202531</t>
+          <t>212514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>259508</t>
+          <t>278211</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252674</t>
+          <t>271271</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>264284</t>
+          <t>283533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>459594</t>
+          <t>487880</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>452386</t>
+          <t>479460</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465364</t>
+          <t>494218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>214421</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>214421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>214421</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>479440</t>
+          <t>509141</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>479440</t>
+          <t>509141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479440</t>
+          <t>509141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46585</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>620883</t>
+          <t>685568</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>611514</t>
+          <t>675901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>628300</t>
+          <t>693278</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>955400</t>
+          <t>819970</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>931358</t>
+          <t>805989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>995333</t>
+          <t>831921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1576283</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1553281</t>
+          <t>1489012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1611627</t>
+          <t>1519932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
